--- a/src/modules/excel/examples/data/form-checkbox.xlsx
+++ b/src/modules/excel/examples/data/form-checkbox.xlsx
@@ -116,23 +116,448 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" fmlaLink="$E$8" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="1" lockText="1" fmlaLink="$E$8" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Unchecked" lockText="1" fmlaLink="$E$10" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="0" lockText="1" fmlaLink="$E$10" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" fmlaLink="$E$12" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="1" lockText="1" fmlaLink="$E$12" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Unchecked" lockText="1" fmlaLink="$E$14" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="0" lockText="1" fmlaLink="$E$14" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Unchecked" lockText="1" fmlaLink="$E$18" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="0" lockText="1" fmlaLink="$E$18" noThreeD="1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="absolute">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>142875</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>276225</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>190500</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Check Box 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="F0F0F0"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="absolute">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>142875</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>276225</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>190500</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1026" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="F0F0F0"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="absolute">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>142875</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>276225</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>190500</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1027" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="F0F0F0"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="absolute">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>142875</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>276225</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>190500</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1028" name="Check Box 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="F0F0F0"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="absolute">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>142875</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>276225</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>190500</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1029" name="Check Box 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1029"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:solidFill>
+                    <a:srgbClr val="F0F0F0"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:ea typeface="Tahoma" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="Tahoma" pitchFamily="2" charset="0"/>
+                </a:rPr>
+                <a:t>I agree to the terms</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" mc:Ignorable="x14ac x14">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -548,7 +973,130 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1025" r:id="rId3" name="Check Box 1">
+              <controlPr locked="0" defaultSize="0" print="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor>
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>142875</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>28575</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>276225</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>190500</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+          <mc:Fallback/>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1026" r:id="rId4" name="Check Box 2">
+              <controlPr locked="0" defaultSize="0" print="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor>
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>142875</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>28575</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>276225</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>190500</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+          <mc:Fallback/>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1027" r:id="rId5" name="Check Box 3">
+              <controlPr locked="0" defaultSize="0" print="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor>
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>142875</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>28575</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>276225</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>190500</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+          <mc:Fallback/>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1028" r:id="rId6" name="Check Box 4">
+              <controlPr locked="0" defaultSize="0" print="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor>
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>142875</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>28575</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>276225</xdr:colOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>190500</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+          <mc:Fallback/>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1029" r:id="rId7" name="Check Box 5">
+              <controlPr locked="0" defaultSize="0" print="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor>
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>142875</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>28575</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>276225</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>190500</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+          <mc:Fallback/>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </worksheet>
 </file>